--- a/output/resumo_por_ano.xlsx
+++ b/output/resumo_por_ano.xlsx
@@ -451,13 +451,13 @@
         <v>2009</v>
       </c>
       <c r="C2" t="n">
-        <v>6399.1</v>
+        <v>19197.3</v>
       </c>
       <c r="D2" t="n">
-        <v>62939.43</v>
+        <v>93911.49000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -465,13 +465,13 @@
         <v>2010</v>
       </c>
       <c r="C3" t="n">
-        <v>6237.1</v>
+        <v>18711.3</v>
       </c>
       <c r="D3" t="n">
-        <v>54357.7</v>
+        <v>84706.05</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -479,13 +479,13 @@
         <v>2011</v>
       </c>
       <c r="C4" t="n">
-        <v>4293</v>
+        <v>12879</v>
       </c>
       <c r="D4" t="n">
-        <v>32728.38</v>
+        <v>52653.96</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -493,13 +493,13 @@
         <v>2012</v>
       </c>
       <c r="C5" t="n">
-        <v>2349</v>
+        <v>7047</v>
       </c>
       <c r="D5" t="n">
-        <v>15705.47</v>
+        <v>26108.46</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -507,13 +507,13 @@
         <v>2013</v>
       </c>
       <c r="C6" t="n">
-        <v>486</v>
+        <v>1458</v>
       </c>
       <c r="D6" t="n">
-        <v>2912.65</v>
+        <v>5091.06</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -524,13 +524,13 @@
         <v>2009</v>
       </c>
       <c r="C7" t="n">
-        <v>15041.07</v>
+        <v>45123.21</v>
       </c>
       <c r="D7" t="n">
-        <v>147138.8</v>
+        <v>219918.63</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -538,13 +538,13 @@
         <v>2010</v>
       </c>
       <c r="C8" t="n">
-        <v>16674.1</v>
+        <v>50022.3</v>
       </c>
       <c r="D8" t="n">
-        <v>145215.06</v>
+        <v>226338.18</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -552,13 +552,13 @@
         <v>2011</v>
       </c>
       <c r="C9" t="n">
-        <v>12548.58</v>
+        <v>37645.74</v>
       </c>
       <c r="D9" t="n">
-        <v>95532.64</v>
+        <v>153733.11</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -566,13 +566,13 @@
         <v>2012</v>
       </c>
       <c r="C10" t="n">
-        <v>8422.98</v>
+        <v>25268.94</v>
       </c>
       <c r="D10" t="n">
-        <v>56104.71</v>
+        <v>93409.23</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -580,13 +580,13 @@
         <v>2013</v>
       </c>
       <c r="C11" t="n">
-        <v>4297.47</v>
+        <v>12892.41</v>
       </c>
       <c r="D11" t="n">
-        <v>25130.84</v>
+        <v>44386.5</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -594,13 +594,13 @@
         <v>2014</v>
       </c>
       <c r="C12" t="n">
-        <v>601.65</v>
+        <v>1804.95</v>
       </c>
       <c r="D12" t="n">
-        <v>3172.48</v>
+        <v>5815.89</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -611,13 +611,13 @@
         <v>2009</v>
       </c>
       <c r="C13" t="n">
-        <v>1826.66</v>
+        <v>5479.98</v>
       </c>
       <c r="D13" t="n">
-        <v>17674.73</v>
+        <v>26517.42</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -625,13 +625,13 @@
         <v>2010</v>
       </c>
       <c r="C14" t="n">
-        <v>2229.94</v>
+        <v>6689.82</v>
       </c>
       <c r="D14" t="n">
-        <v>19477.73</v>
+        <v>30331.47</v>
       </c>
       <c r="E14" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -639,13 +639,13 @@
         <v>2011</v>
       </c>
       <c r="C15" t="n">
-        <v>1091.25</v>
+        <v>3273.75</v>
       </c>
       <c r="D15" t="n">
-        <v>8373.99</v>
+        <v>13457.04</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -653,13 +653,13 @@
         <v>2012</v>
       </c>
       <c r="C16" t="n">
-        <v>118.62</v>
+        <v>355.86</v>
       </c>
       <c r="D16" t="n">
-        <v>823.04</v>
+        <v>1349.25</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -670,13 +670,13 @@
         <v>2009</v>
       </c>
       <c r="C17" t="n">
-        <v>3231.84</v>
+        <v>9474.059999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>31050.97</v>
+        <v>45638.87</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -684,13 +684,13 @@
         <v>2010</v>
       </c>
       <c r="C18" t="n">
-        <v>6351.48</v>
+        <v>18619.18</v>
       </c>
       <c r="D18" t="n">
-        <v>55207.86</v>
+        <v>84134.78999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -698,13 +698,13 @@
         <v>2011</v>
       </c>
       <c r="C19" t="n">
-        <v>5431.33</v>
+        <v>15921.74</v>
       </c>
       <c r="D19" t="n">
-        <v>41288.68</v>
+        <v>64941.09</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -712,13 +712,13 @@
         <v>2012</v>
       </c>
       <c r="C20" t="n">
-        <v>4354.03</v>
+        <v>12763.69</v>
       </c>
       <c r="D20" t="n">
-        <v>28923.45</v>
+        <v>47106.29</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
@@ -726,13 +726,13 @@
         <v>2013</v>
       </c>
       <c r="C21" t="n">
-        <v>3276.76</v>
+        <v>9605.700000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>19027.88</v>
+        <v>32935.53</v>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
@@ -740,13 +740,13 @@
         <v>2014</v>
       </c>
       <c r="C22" t="n">
-        <v>2199.45</v>
+        <v>6447.62</v>
       </c>
       <c r="D22" t="n">
-        <v>11174.74</v>
+        <v>20196.91</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -754,13 +754,13 @@
         <v>2015</v>
       </c>
       <c r="C23" t="n">
-        <v>1122.18</v>
+        <v>3289.62</v>
       </c>
       <c r="D23" t="n">
-        <v>5005.47</v>
+        <v>9259.889999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24">
@@ -768,13 +768,13 @@
         <v>2016</v>
       </c>
       <c r="C24" t="n">
-        <v>157.1</v>
+        <v>460.54</v>
       </c>
       <c r="D24" t="n">
-        <v>631.89</v>
+        <v>1174.86</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -785,13 +785,13 @@
         <v>2009</v>
       </c>
       <c r="C25" t="n">
-        <v>2738.65</v>
+        <v>8215.950000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>26162.9</v>
+        <v>39437.97</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -799,13 +799,13 @@
         <v>2010</v>
       </c>
       <c r="C26" t="n">
-        <v>5945.18</v>
+        <v>17835.54</v>
       </c>
       <c r="D26" t="n">
-        <v>51787.23</v>
+        <v>80713.14</v>
       </c>
       <c r="E26" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
@@ -813,13 +813,13 @@
         <v>2011</v>
       </c>
       <c r="C27" t="n">
-        <v>4313.4</v>
+        <v>12940.2</v>
       </c>
       <c r="D27" t="n">
-        <v>32857.2</v>
+        <v>52869.06</v>
       </c>
       <c r="E27" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
@@ -827,13 +827,13 @@
         <v>2012</v>
       </c>
       <c r="C28" t="n">
-        <v>2670.21</v>
+        <v>8010.63</v>
       </c>
       <c r="D28" t="n">
-        <v>17810.82</v>
+        <v>29636.85</v>
       </c>
       <c r="E28" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
@@ -841,13 +841,13 @@
         <v>2013</v>
       </c>
       <c r="C29" t="n">
-        <v>1026.99</v>
+        <v>3080.97</v>
       </c>
       <c r="D29" t="n">
-        <v>6048.34</v>
+        <v>10651.32</v>
       </c>
       <c r="E29" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
@@ -855,13 +855,13 @@
         <v>2014</v>
       </c>
       <c r="C30" t="n">
-        <v>11.41</v>
+        <v>34.23</v>
       </c>
       <c r="D30" t="n">
-        <v>61.31</v>
+        <v>111.81</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -872,13 +872,13 @@
         <v>2009</v>
       </c>
       <c r="C31" t="n">
-        <v>3344.68</v>
+        <v>9743.6</v>
       </c>
       <c r="D31" t="n">
-        <v>31770.9</v>
+        <v>46608.72</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
@@ -886,13 +886,13 @@
         <v>2010</v>
       </c>
       <c r="C32" t="n">
-        <v>9406.9</v>
+        <v>27403.83</v>
       </c>
       <c r="D32" t="n">
-        <v>81872.12</v>
+        <v>123941.31</v>
       </c>
       <c r="E32" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33">
@@ -900,13 +900,13 @@
         <v>2011</v>
       </c>
       <c r="C33" t="n">
-        <v>7441.9</v>
+        <v>21679.46</v>
       </c>
       <c r="D33" t="n">
-        <v>56618.1</v>
+        <v>88483.64999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34">
@@ -914,13 +914,13 @@
         <v>2012</v>
       </c>
       <c r="C34" t="n">
-        <v>5435.1</v>
+        <v>15833.32</v>
       </c>
       <c r="D34" t="n">
-        <v>36153.94</v>
+        <v>58482.61</v>
       </c>
       <c r="E34" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35">
@@ -928,13 +928,13 @@
         <v>2013</v>
       </c>
       <c r="C35" t="n">
-        <v>3428.29</v>
+        <v>9987.16</v>
       </c>
       <c r="D35" t="n">
-        <v>19964.89</v>
+        <v>34300.71</v>
       </c>
       <c r="E35" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36">
@@ -942,13 +942,13 @@
         <v>2014</v>
       </c>
       <c r="C36" t="n">
-        <v>1421.49</v>
+        <v>4141.03</v>
       </c>
       <c r="D36" t="n">
-        <v>7296.3</v>
+        <v>13073.74</v>
       </c>
       <c r="E36" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37">
@@ -956,13 +956,13 @@
         <v>2015</v>
       </c>
       <c r="C37" t="n">
-        <v>41.81</v>
+        <v>121.8</v>
       </c>
       <c r="D37" t="n">
-        <v>195.44</v>
+        <v>357.36</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -973,13 +973,13 @@
         <v>2009</v>
       </c>
       <c r="C38" t="n">
-        <v>1059.49</v>
+        <v>3178.47</v>
       </c>
       <c r="D38" t="n">
-        <v>10010.35</v>
+        <v>15154.62</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -987,13 +987,13 @@
         <v>2010</v>
       </c>
       <c r="C39" t="n">
-        <v>2856</v>
+        <v>8568</v>
       </c>
       <c r="D39" t="n">
-        <v>25019.51</v>
+        <v>38926.29</v>
       </c>
       <c r="E39" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40">
@@ -1001,13 +1001,13 @@
         <v>2011</v>
       </c>
       <c r="C40" t="n">
-        <v>690.95</v>
+        <v>2072.85</v>
       </c>
       <c r="D40" t="n">
-        <v>5408.94</v>
+        <v>8662.35</v>
       </c>
       <c r="E40" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
@@ -1018,13 +1018,13 @@
         <v>2009</v>
       </c>
       <c r="C41" t="n">
-        <v>1944.02</v>
+        <v>5832.06</v>
       </c>
       <c r="D41" t="n">
-        <v>18257.81</v>
+        <v>27704.91</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -1032,13 +1032,13 @@
         <v>2010</v>
       </c>
       <c r="C42" t="n">
-        <v>10179.12</v>
+        <v>30537.36</v>
       </c>
       <c r="D42" t="n">
-        <v>88768.45</v>
+        <v>138302.85</v>
       </c>
       <c r="E42" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43">
@@ -1046,13 +1046,13 @@
         <v>2011</v>
       </c>
       <c r="C43" t="n">
-        <v>6318.08</v>
+        <v>18954.24</v>
       </c>
       <c r="D43" t="n">
-        <v>48253.56</v>
+        <v>77607.60000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44">
@@ -1060,13 +1060,13 @@
         <v>2012</v>
       </c>
       <c r="C44" t="n">
-        <v>2430</v>
+        <v>7290</v>
       </c>
       <c r="D44" t="n">
-        <v>16386.34</v>
+        <v>27147.09</v>
       </c>
       <c r="E44" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45">
@@ -1074,13 +1074,13 @@
         <v>2013</v>
       </c>
       <c r="C45" t="n">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="D45" t="n">
-        <v>166.09</v>
+        <v>286.62</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -1091,13 +1091,13 @@
         <v>2009</v>
       </c>
       <c r="C46" t="n">
-        <v>1443.94</v>
+        <v>4331.82</v>
       </c>
       <c r="D46" t="n">
-        <v>13484.68</v>
+        <v>20506.95</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1105,13 +1105,13 @@
         <v>2010</v>
       </c>
       <c r="C47" t="n">
-        <v>16695.58</v>
+        <v>50086.74</v>
       </c>
       <c r="D47" t="n">
-        <v>145235.82</v>
+        <v>226456.08</v>
       </c>
       <c r="E47" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48">
@@ -1119,13 +1119,13 @@
         <v>2011</v>
       </c>
       <c r="C48" t="n">
-        <v>12815</v>
+        <v>38445</v>
       </c>
       <c r="D48" t="n">
-        <v>97571.16</v>
+        <v>157010.46</v>
       </c>
       <c r="E48" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49">
@@ -1133,13 +1133,13 @@
         <v>2012</v>
       </c>
       <c r="C49" t="n">
-        <v>8483.17</v>
+        <v>25449.51</v>
       </c>
       <c r="D49" t="n">
-        <v>56518.57</v>
+        <v>94089.75</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50">
@@ -1147,13 +1147,13 @@
         <v>2013</v>
       </c>
       <c r="C50" t="n">
-        <v>4151.34</v>
+        <v>12454.02</v>
       </c>
       <c r="D50" t="n">
-        <v>24298.82</v>
+        <v>42900.48</v>
       </c>
       <c r="E50" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51">
@@ -1161,13 +1161,13 @@
         <v>2014</v>
       </c>
       <c r="C51" t="n">
-        <v>451.23</v>
+        <v>1353.69</v>
       </c>
       <c r="D51" t="n">
-        <v>2388.24</v>
+        <v>4373.79</v>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
@@ -1178,13 +1178,13 @@
         <v>2010</v>
       </c>
       <c r="C52" t="n">
-        <v>1962</v>
+        <v>5886</v>
       </c>
       <c r="D52" t="n">
-        <v>17163.69</v>
+        <v>26715.51</v>
       </c>
       <c r="E52" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53">
@@ -1192,13 +1192,13 @@
         <v>2011</v>
       </c>
       <c r="C53" t="n">
-        <v>689.35</v>
+        <v>2068.05</v>
       </c>
       <c r="D53" t="n">
-        <v>5336.93</v>
+        <v>8563.41</v>
       </c>
       <c r="E53" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54">
@@ -1209,13 +1209,13 @@
         <v>2010</v>
       </c>
       <c r="C54" t="n">
-        <v>18554.14</v>
+        <v>54655.48</v>
       </c>
       <c r="D54" t="n">
-        <v>160215.55</v>
+        <v>245906.84</v>
       </c>
       <c r="E54" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55">
@@ -1223,13 +1223,13 @@
         <v>2011</v>
       </c>
       <c r="C55" t="n">
-        <v>19136.48</v>
+        <v>56370.87</v>
       </c>
       <c r="D55" t="n">
-        <v>145388.15</v>
+        <v>229811.09</v>
       </c>
       <c r="E55" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56">
@@ -1237,13 +1237,13 @@
         <v>2012</v>
       </c>
       <c r="C56" t="n">
-        <v>16265.03</v>
+        <v>47912.32</v>
       </c>
       <c r="D56" t="n">
-        <v>107962.75</v>
+        <v>176745.58</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57">
@@ -1251,13 +1251,13 @@
         <v>2013</v>
       </c>
       <c r="C57" t="n">
-        <v>13373.4</v>
+        <v>39394.44</v>
       </c>
       <c r="D57" t="n">
-        <v>77561.14999999999</v>
+        <v>134974.77</v>
       </c>
       <c r="E57" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58">
@@ -1265,13 +1265,13 @@
         <v>2014</v>
       </c>
       <c r="C58" t="n">
-        <v>10481.88</v>
+        <v>30876.78</v>
       </c>
       <c r="D58" t="n">
-        <v>53128.11</v>
+        <v>96543.55</v>
       </c>
       <c r="E58" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59">
@@ -1279,13 +1279,13 @@
         <v>2015</v>
       </c>
       <c r="C59" t="n">
-        <v>7590.36</v>
+        <v>22359.1</v>
       </c>
       <c r="D59" t="n">
-        <v>33639.51</v>
+        <v>62562.97</v>
       </c>
       <c r="E59" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="60">
@@ -1293,13 +1293,13 @@
         <v>2016</v>
       </c>
       <c r="C60" t="n">
-        <v>4698.77</v>
+        <v>13841.32</v>
       </c>
       <c r="D60" t="n">
-        <v>18234.87</v>
+        <v>34096.87</v>
       </c>
       <c r="E60" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61">
@@ -1307,13 +1307,13 @@
         <v>2017</v>
       </c>
       <c r="C61" t="n">
-        <v>1807.2</v>
+        <v>5323.52</v>
       </c>
       <c r="D61" t="n">
-        <v>6192.35</v>
+        <v>11710.96</v>
       </c>
       <c r="E61" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62">
@@ -1321,13 +1321,13 @@
         <v>2018</v>
       </c>
       <c r="C62" t="n">
-        <v>20.08</v>
+        <v>59.15</v>
       </c>
       <c r="D62" t="n">
-        <v>62.76</v>
+        <v>122.83</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -1338,13 +1338,13 @@
         <v>2010</v>
       </c>
       <c r="C63" t="n">
-        <v>7698.34</v>
+        <v>23095.02</v>
       </c>
       <c r="D63" t="n">
-        <v>66122.48</v>
+        <v>103550.1</v>
       </c>
       <c r="E63" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64">
@@ -1352,13 +1352,13 @@
         <v>2011</v>
       </c>
       <c r="C64" t="n">
-        <v>7853.88</v>
+        <v>23561.64</v>
       </c>
       <c r="D64" t="n">
-        <v>59730.81</v>
+        <v>96137.31</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -1366,13 +1366,13 @@
         <v>2012</v>
       </c>
       <c r="C65" t="n">
-        <v>5987.61</v>
+        <v>17962.83</v>
       </c>
       <c r="D65" t="n">
-        <v>39803.5</v>
+        <v>66322.89</v>
       </c>
       <c r="E65" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66">
@@ -1380,13 +1380,13 @@
         <v>2013</v>
       </c>
       <c r="C66" t="n">
-        <v>4121.28</v>
+        <v>12363.84</v>
       </c>
       <c r="D66" t="n">
-        <v>23965.41</v>
+        <v>42426.78</v>
       </c>
       <c r="E66" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67">
@@ -1394,13 +1394,13 @@
         <v>2014</v>
       </c>
       <c r="C67" t="n">
-        <v>2255.04</v>
+        <v>6765.12</v>
       </c>
       <c r="D67" t="n">
-        <v>11500.38</v>
+        <v>21252.6</v>
       </c>
       <c r="E67" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="68">
@@ -1408,13 +1408,13 @@
         <v>2015</v>
       </c>
       <c r="C68" t="n">
-        <v>466.56</v>
+        <v>1399.68</v>
       </c>
       <c r="D68" t="n">
-        <v>2132.79</v>
+        <v>4029.87</v>
       </c>
       <c r="E68" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69">
@@ -1425,13 +1425,13 @@
         <v>2010</v>
       </c>
       <c r="C69" t="n">
-        <v>5674.78</v>
+        <v>17024.34</v>
       </c>
       <c r="D69" t="n">
-        <v>48494.03</v>
+        <v>76066.32000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70">
@@ -1439,13 +1439,13 @@
         <v>2011</v>
       </c>
       <c r="C70" t="n">
-        <v>5960.57</v>
+        <v>17881.71</v>
       </c>
       <c r="D70" t="n">
-        <v>45378</v>
+        <v>73023.14999999999</v>
       </c>
       <c r="E70" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71">
@@ -1453,13 +1453,13 @@
         <v>2012</v>
       </c>
       <c r="C71" t="n">
-        <v>4000.92</v>
+        <v>12002.76</v>
       </c>
       <c r="D71" t="n">
-        <v>26649.72</v>
+        <v>44369.43</v>
       </c>
       <c r="E71" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="72">
@@ -1467,13 +1467,13 @@
         <v>2013</v>
       </c>
       <c r="C72" t="n">
-        <v>2041.29</v>
+        <v>6123.87</v>
       </c>
       <c r="D72" t="n">
-        <v>11937.14</v>
+        <v>21083.52</v>
       </c>
       <c r="E72" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73">
@@ -1481,13 +1481,13 @@
         <v>2014</v>
       </c>
       <c r="C73" t="n">
-        <v>285.78</v>
+        <v>857.34</v>
       </c>
       <c r="D73" t="n">
-        <v>1506.93</v>
+        <v>2762.52</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74">
@@ -1498,13 +1498,13 @@
         <v>2010</v>
       </c>
       <c r="C74" t="n">
-        <v>15973.9</v>
+        <v>47921.7</v>
       </c>
       <c r="D74" t="n">
-        <v>135588.41</v>
+        <v>213100.5</v>
       </c>
       <c r="E74" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75">
@@ -1512,13 +1512,13 @@
         <v>2011</v>
       </c>
       <c r="C75" t="n">
-        <v>21502.28</v>
+        <v>64506.84</v>
       </c>
       <c r="D75" t="n">
-        <v>163436.9</v>
+        <v>263078.61</v>
       </c>
       <c r="E75" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="76">
@@ -1526,13 +1526,13 @@
         <v>2012</v>
       </c>
       <c r="C76" t="n">
-        <v>17501.86</v>
+        <v>52505.58</v>
       </c>
       <c r="D76" t="n">
-        <v>116238.67</v>
+        <v>193755.39</v>
       </c>
       <c r="E76" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77">
@@ -1540,13 +1540,13 @@
         <v>2013</v>
       </c>
       <c r="C77" t="n">
-        <v>13501.44</v>
+        <v>40504.32</v>
       </c>
       <c r="D77" t="n">
-        <v>78373.50999999999</v>
+        <v>138849.93</v>
       </c>
       <c r="E77" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="78">
@@ -1554,13 +1554,13 @@
         <v>2014</v>
       </c>
       <c r="C78" t="n">
-        <v>9501</v>
+        <v>28503</v>
       </c>
       <c r="D78" t="n">
-        <v>48234.55</v>
+        <v>89232.06</v>
       </c>
       <c r="E78" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79">
@@ -1568,13 +1568,13 @@
         <v>2015</v>
       </c>
       <c r="C79" t="n">
-        <v>5500.58</v>
+        <v>16501.74</v>
       </c>
       <c r="D79" t="n">
-        <v>24472.15</v>
+        <v>46339.02</v>
       </c>
       <c r="E79" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="80">
@@ -1582,13 +1582,13 @@
         <v>2016</v>
       </c>
       <c r="C80" t="n">
-        <v>1527.94</v>
+        <v>4583.82</v>
       </c>
       <c r="D80" t="n">
-        <v>6055.2</v>
+        <v>11525.43</v>
       </c>
       <c r="E80" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81">
@@ -1599,13 +1599,13 @@
         <v>2010</v>
       </c>
       <c r="C81" t="n">
-        <v>2191.98</v>
+        <v>6575.94</v>
       </c>
       <c r="D81" t="n">
-        <v>18523.74</v>
+        <v>29148.69</v>
       </c>
       <c r="E81" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82">
@@ -1613,13 +1613,13 @@
         <v>2011</v>
       </c>
       <c r="C82" t="n">
-        <v>2675.93</v>
+        <v>8027.79</v>
       </c>
       <c r="D82" t="n">
-        <v>20413.34</v>
+        <v>32837.94</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="83">
@@ -1627,13 +1627,13 @@
         <v>2012</v>
       </c>
       <c r="C83" t="n">
-        <v>1309.5</v>
+        <v>3928.5</v>
       </c>
       <c r="D83" t="n">
-        <v>8776.24</v>
+        <v>14575.56</v>
       </c>
       <c r="E83" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="84">
@@ -1641,13 +1641,13 @@
         <v>2013</v>
       </c>
       <c r="C84" t="n">
-        <v>142.35</v>
+        <v>427.05</v>
       </c>
       <c r="D84" t="n">
-        <v>862.6</v>
+        <v>1499.85</v>
       </c>
       <c r="E84" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85">
@@ -1658,13 +1658,13 @@
         <v>2010</v>
       </c>
       <c r="C85" t="n">
-        <v>5087.2</v>
+        <v>14912.95</v>
       </c>
       <c r="D85" t="n">
-        <v>42444.29</v>
+        <v>65473.16</v>
       </c>
       <c r="E85" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86">
@@ -1672,13 +1672,13 @@
         <v>2011</v>
       </c>
       <c r="C86" t="n">
-        <v>12039.7</v>
+        <v>35293.96</v>
       </c>
       <c r="D86" t="n">
-        <v>91386.78999999999</v>
+        <v>143776.42</v>
       </c>
       <c r="E86" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87">
@@ -1686,13 +1686,13 @@
         <v>2012</v>
       </c>
       <c r="C87" t="n">
-        <v>10072.64</v>
+        <v>29527.6</v>
       </c>
       <c r="D87" t="n">
-        <v>66907.85000000001</v>
+        <v>108972.34</v>
       </c>
       <c r="E87" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="88">
@@ -1700,13 +1700,13 @@
         <v>2013</v>
       </c>
       <c r="C88" t="n">
-        <v>7630.78</v>
+        <v>22369.34</v>
       </c>
       <c r="D88" t="n">
-        <v>44307.15</v>
+        <v>76694.53999999999</v>
       </c>
       <c r="E88" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="89">
@@ -1714,13 +1714,13 @@
         <v>2014</v>
       </c>
       <c r="C89" t="n">
-        <v>5188.94</v>
+        <v>15211.18</v>
       </c>
       <c r="D89" t="n">
-        <v>26357.65</v>
+        <v>47640.54</v>
       </c>
       <c r="E89" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="90">
@@ -1728,13 +1728,13 @@
         <v>2015</v>
       </c>
       <c r="C90" t="n">
-        <v>2747.08</v>
+        <v>8052.98</v>
       </c>
       <c r="D90" t="n">
-        <v>12243.75</v>
+        <v>22651.51</v>
       </c>
       <c r="E90" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="91">
@@ -1742,13 +1742,13 @@
         <v>2016</v>
       </c>
       <c r="C91" t="n">
-        <v>474.8</v>
+        <v>1391.88</v>
       </c>
       <c r="D91" t="n">
-        <v>1902.62</v>
+        <v>3537.9</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92">
@@ -1759,13 +1759,13 @@
         <v>2010</v>
       </c>
       <c r="C92" t="n">
-        <v>2142.24</v>
+        <v>6426.72</v>
       </c>
       <c r="D92" t="n">
-        <v>17772.15</v>
+        <v>28097.13</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93">
@@ -1773,13 +1773,13 @@
         <v>2011</v>
       </c>
       <c r="C93" t="n">
-        <v>5266.34</v>
+        <v>15799.02</v>
       </c>
       <c r="D93" t="n">
-        <v>40127.87</v>
+        <v>64564.56</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="94">
@@ -1787,13 +1787,13 @@
         <v>2012</v>
       </c>
       <c r="C94" t="n">
-        <v>3124.1</v>
+        <v>9372.299999999999</v>
       </c>
       <c r="D94" t="n">
-        <v>20854.78</v>
+        <v>34690.83</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="95">
@@ -1801,13 +1801,13 @@
         <v>2013</v>
       </c>
       <c r="C95" t="n">
-        <v>981.86</v>
+        <v>2945.58</v>
       </c>
       <c r="D95" t="n">
-        <v>5819.53</v>
+        <v>10221.57</v>
       </c>
       <c r="E95" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96">
@@ -1818,13 +1818,13 @@
         <v>2010</v>
       </c>
       <c r="C96" t="n">
-        <v>3197.31</v>
+        <v>9591.93</v>
       </c>
       <c r="D96" t="n">
-        <v>26374.72</v>
+        <v>41760.54</v>
       </c>
       <c r="E96" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97">
@@ -1832,13 +1832,13 @@
         <v>2011</v>
       </c>
       <c r="C97" t="n">
-        <v>11989.89</v>
+        <v>35969.67</v>
       </c>
       <c r="D97" t="n">
-        <v>91160.33</v>
+        <v>146731.2</v>
       </c>
       <c r="E97" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98">
@@ -1846,13 +1846,13 @@
         <v>2012</v>
       </c>
       <c r="C98" t="n">
-        <v>8925.809999999999</v>
+        <v>26777.43</v>
       </c>
       <c r="D98" t="n">
-        <v>59366.68</v>
+        <v>98898.96000000001</v>
       </c>
       <c r="E98" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="99">
@@ -1860,13 +1860,13 @@
         <v>2013</v>
       </c>
       <c r="C99" t="n">
-        <v>5728.5</v>
+        <v>17185.5</v>
       </c>
       <c r="D99" t="n">
-        <v>33350.2</v>
+        <v>59012.85</v>
       </c>
       <c r="E99" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="100">
@@ -1874,13 +1874,13 @@
         <v>2014</v>
       </c>
       <c r="C100" t="n">
-        <v>2531.19</v>
+        <v>7593.57</v>
       </c>
       <c r="D100" t="n">
-        <v>12971</v>
+        <v>23943.66</v>
       </c>
       <c r="E100" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101">
@@ -1888,13 +1888,13 @@
         <v>2015</v>
       </c>
       <c r="C101" t="n">
-        <v>133.22</v>
+        <v>399.66</v>
       </c>
       <c r="D101" t="n">
-        <v>620.42</v>
+        <v>1169.07</v>
       </c>
       <c r="E101" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
@@ -1905,13 +1905,13 @@
         <v>2010</v>
       </c>
       <c r="C102" t="n">
-        <v>3200.34</v>
+        <v>9601.02</v>
       </c>
       <c r="D102" t="n">
-        <v>26250.54</v>
+        <v>41629.08</v>
       </c>
       <c r="E102" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
@@ -1919,13 +1919,13 @@
         <v>2011</v>
       </c>
       <c r="C103" t="n">
-        <v>18455.28</v>
+        <v>55365.84</v>
       </c>
       <c r="D103" t="n">
-        <v>140207.67</v>
+        <v>225708.03</v>
       </c>
       <c r="E103" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="104">
@@ -1933,13 +1933,13 @@
         <v>2012</v>
       </c>
       <c r="C104" t="n">
-        <v>14881.59</v>
+        <v>44644.77</v>
       </c>
       <c r="D104" t="n">
-        <v>98868.64999999999</v>
+        <v>164779.77</v>
       </c>
       <c r="E104" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105">
@@ -1947,13 +1947,13 @@
         <v>2013</v>
       </c>
       <c r="C105" t="n">
-        <v>11041.15</v>
+        <v>33123.45</v>
       </c>
       <c r="D105" t="n">
-        <v>64128.99</v>
+        <v>113586.21</v>
       </c>
       <c r="E105" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="106">
@@ -1961,13 +1961,13 @@
         <v>2014</v>
       </c>
       <c r="C106" t="n">
-        <v>7200.78</v>
+        <v>21602.34</v>
       </c>
       <c r="D106" t="n">
-        <v>36602.47</v>
+        <v>67693.64999999999</v>
       </c>
       <c r="E106" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="107">
@@ -1975,13 +1975,13 @@
         <v>2015</v>
       </c>
       <c r="C107" t="n">
-        <v>3360.35</v>
+        <v>10081.05</v>
       </c>
       <c r="D107" t="n">
-        <v>15019.28</v>
+        <v>28430.25</v>
       </c>
       <c r="E107" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="108">
@@ -1989,13 +1989,13 @@
         <v>2016</v>
       </c>
       <c r="C108" t="n">
-        <v>266.7</v>
+        <v>800.1</v>
       </c>
       <c r="D108" t="n">
-        <v>1080.68</v>
+        <v>2055.78</v>
       </c>
       <c r="E108" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109">
@@ -2006,13 +2006,13 @@
         <v>2010</v>
       </c>
       <c r="C109" t="n">
-        <v>712.8099999999999</v>
+        <v>2138.43</v>
       </c>
       <c r="D109" t="n">
-        <v>5813.76</v>
+        <v>9232.889999999999</v>
       </c>
       <c r="E109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -2020,13 +2020,13 @@
         <v>2011</v>
       </c>
       <c r="C110" t="n">
-        <v>7395.42</v>
+        <v>22186.26</v>
       </c>
       <c r="D110" t="n">
-        <v>56276.42</v>
+        <v>90568.53</v>
       </c>
       <c r="E110" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="111">
@@ -2034,13 +2034,13 @@
         <v>2012</v>
       </c>
       <c r="C111" t="n">
-        <v>5256.95</v>
+        <v>15770.85</v>
       </c>
       <c r="D111" t="n">
-        <v>34983.62</v>
+        <v>58266.45</v>
       </c>
       <c r="E111" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="112">
@@ -2048,13 +2048,13 @@
         <v>2013</v>
       </c>
       <c r="C112" t="n">
-        <v>3118.5</v>
+        <v>9355.5</v>
       </c>
       <c r="D112" t="n">
-        <v>18181.27</v>
+        <v>32152.2</v>
       </c>
       <c r="E112" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="113">
@@ -2062,13 +2062,13 @@
         <v>2014</v>
       </c>
       <c r="C113" t="n">
-        <v>980.1</v>
+        <v>2940.3</v>
       </c>
       <c r="D113" t="n">
-        <v>5073.49</v>
+        <v>9343.469999999999</v>
       </c>
       <c r="E113" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
